--- a/samples/datamodel_template_v1.xlsx
+++ b/samples/datamodel_template_v1.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Model" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Model!$A$1:$AT$1</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Model!$A$1:$AR$1</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">Namespace</t>
   </si>
@@ -64,9 +64,6 @@
     <t xml:space="preserve">ModelParent</t>
   </si>
   <si>
-    <t xml:space="preserve">EntityNamespace</t>
-  </si>
-  <si>
     <t xml:space="preserve">Entity</t>
   </si>
   <si>
@@ -109,9 +106,6 @@
     <t xml:space="preserve">EntityKeyAttributes</t>
   </si>
   <si>
-    <t xml:space="preserve">RelationshipNamespace</t>
-  </si>
-  <si>
     <t xml:space="preserve">Relationship</t>
   </si>
   <si>
@@ -142,7 +136,7 @@
     <t xml:space="preserve">SourceRoleCardinality</t>
   </si>
   <si>
-    <t xml:space="preserve">TargetEntityNamespace</t>
+    <t xml:space="preserve">TargetEntityModel</t>
   </si>
   <si>
     <t xml:space="preserve">TargetRoleEntity</t>
@@ -414,38 +408,37 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="6.85"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="28.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="23.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="23.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="24.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="2" width="23.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="17.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="25.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="15.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="13.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="27.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="2" width="24.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="23.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="29" style="1" width="25.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="17.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="2" width="25.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="21.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="20.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="18.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="16.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="14.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="18.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="20.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="16.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="14.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="10.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="15.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="14.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="18.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="20.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="17.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="18.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="23.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="23.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="24.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="23.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="17.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="25.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="13.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="20.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="27.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="2" width="24.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="23.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="25.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="17.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="2" width="25.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="21.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="20.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="18.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="16.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="14.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="18.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="20.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="16.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="14.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="10.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="14.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="18.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="20.22"/>
   </cols>
   <sheetData>
     <row r="1" s="3" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -494,19 +487,19 @@
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="3" t="s">
@@ -524,10 +517,10 @@
       <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
       <c r="AB1" s="3" t="s">
@@ -536,13 +529,13 @@
       <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="3" t="s">
@@ -581,15 +574,11 @@
       <c r="AR1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="3" t="s">
-        <v>45</v>
-      </c>
+      <c r="AS1" s="0"/>
+      <c r="AT1" s="0"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT1"/>
+  <autoFilter ref="A1:AR1"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
